--- a/mock/外呼活动 mock 数据.xlsx
+++ b/mock/外呼活动 mock 数据.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1336,7 +1336,7 @@
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
-  "活动状态": "已结束"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -1644,7 +1644,7 @@
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
-  "活动状态": "已结束"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -1952,7 +1952,7 @@
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
-  "活动状态": "已结束"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -2243,12 +2243,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>ACT20250605104812</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250605104812"
@@ -2260,7 +2260,7 @@
   "活动审核通过时间": "2025-06-04 15:22:10"
   "活动开始时间": "2025-06-04 15:22:10"
   "活动结束时间": "2025-06-30 23:59:59"
-  "活动状态": "已发布进行中"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -2270,7 +2270,7 @@
 }</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250605104812"
@@ -2296,7 +2296,7 @@
 }</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -2316,7 +2316,7 @@
 }</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -2336,7 +2336,7 @@
 }</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -2356,7 +2356,7 @@
 }</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"
@@ -2376,7 +2376,7 @@
 }</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250605104812"
@@ -2385,7 +2385,7 @@
 }</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250605104812"
@@ -2399,7 +2399,7 @@
 }</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250605104812"
@@ -2413,7 +2413,7 @@
 }</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -2447,7 +2447,7 @@
 }</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -2481,7 +2481,7 @@
 }</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -2515,7 +2515,7 @@
 }</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"
@@ -2551,12 +2551,12 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>ACT20250410104126</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250410104126"
@@ -2568,7 +2568,7 @@
   "活动审核通过时间": "2025-04-09 10:08:45"
   "活动开始时间": "2025-04-09 10:08:45"
   "活动结束时间": "2025-05-10 23:59:59"
-  "活动状态": "已结束"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -2578,7 +2578,7 @@
 }</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250410104126"
@@ -2604,7 +2604,7 @@
 }</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -2624,7 +2624,7 @@
 }</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -2644,7 +2644,7 @@
 }</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -2664,7 +2664,7 @@
 }</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"
@@ -2684,7 +2684,7 @@
 }</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250410104126"
@@ -2693,7 +2693,7 @@
 }</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250410104126"
@@ -2707,7 +2707,7 @@
 }</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250410104126"
@@ -2721,7 +2721,7 @@
 }</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -2755,7 +2755,7 @@
 }</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -2789,7 +2789,7 @@
 }</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -2823,7 +2823,7 @@
 }</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"
@@ -2859,12 +2859,12 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>ACT20250520104605</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250520104605"
@@ -2876,7 +2876,7 @@
   "活动审核通过时间": "2025-05-19 14:36:20"
   "活动开始时间": "2025-05-19 14:36:20"
   "活动结束时间": "2025-06-20 23:59:59"
-  "活动状态": "已发布进行中"
+  "活动状态": "活动结束"
   "活动目标": "老客户提升销售"
   "创建人编号": "1017553"
   "创建人名称": "余小姐"
@@ -2886,7 +2886,7 @@
 }</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250520104605"
@@ -2912,7 +2912,7 @@
 }</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -2932,7 +2932,7 @@
 }</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -2952,7 +2952,7 @@
 }</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -2972,7 +2972,7 @@
 }</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"
@@ -2992,7 +2992,7 @@
 }</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250520104605"
@@ -3001,7 +3001,7 @@
 }</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250520104605"
@@ -3015,7 +3015,7 @@
 }</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>{
   "act_no": "ACT20250520104605"
@@ -3029,7 +3029,7 @@
 }</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "外呼所有客户"
@@ -3063,7 +3063,7 @@
 }</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系成功客户"
@@ -3097,7 +3097,7 @@
 }</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "联系失败客户"
@@ -3131,7 +3131,7 @@
 }</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="0" t="inlineStr">
         <is>
           <t>{
   "客群范围": "有效通话客户"

--- a/mock/外呼活动 mock 数据.xlsx
+++ b/mock/外呼活动 mock 数据.xlsx
@@ -1332,7 +1332,7 @@
   "act_proc_no": "ACT2026011690656801"
   "push_task_name": "26年1月无新开户有存款意向"
   "push_task_remark": "开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
@@ -1350,7 +1350,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "yewu_type": "财富类"
   "外呼执行天数": 59
   "外呼人数": 6538
@@ -1377,7 +1377,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "外呼人数": 6538
   "外呼7日内点击理财人数": 351
   "外呼7日内购买理财人数": 76
@@ -1397,7 +1397,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "联系失败人数": 2843
   "外呼7日内点击理财人数": 120
   "外呼7日内购买理财人数": 24
@@ -1417,7 +1417,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "有效通话人数": 3695
   "外呼7日内点击理财人数": 231
   "外呼7日内购买理财人数": 52
@@ -1437,7 +1437,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "有效通话人数": 4849
   "外呼7日内点击理财人数": 260
   "外呼7日内购买理财人数": 57
@@ -1456,7 +1456,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "购买产品top10": "{产品类型:存款，产品名称：1到3年期普通定期，购买人数：39，购买人数排序：1，购买金额：3014525.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有7天11号-A份额（南京银行行庆专属），购买人数：19，购买人数排序：2，购买金额：327817.00，购买金额排序：4},{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额（南京银行行庆专属），购买人数：7，购买人数排序：3，购买金额：530000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财财富牛最低持有28天1号-A份额，购买人数：7，购买人数排序：4，购买金额：86717.00，购买金额排序：9},{产品类型:存款，产品名称：1年以内普通定期，购买人数：5，购买人数排序：5，购买金额：185150.00，购买金额排序：6},{产品类型:理财，产品名称：南银理财日日聚宝12号-A份额，购买人数：3，购买人数排序：6，购买金额：17839.00，购买金额排序：23},{产品类型:理财，产品名称：南银理财悦稳最低持有60天4号-A份额，购买人数：2，购买人数排序：7，购买金额：17899.00，购买金额排序：22},{产品类型:理财，产品名称：南银理财鼎瑞悦稳天添盈4号-A份额，购买人数：2，购买人数排序：8，购买金额：11347.00，购买金额排序：26},{产品类型:理财，产品名称：南银理财悦稳最低持有14天4号-A份额，购买人数：2，购买人数排序：9，购买金额：20000.00，购买金额排序：20},{产品类型:理财，产品名称：南银理财日日聚宝4号-A份额，购买人数：2，购买人数排序：10，购买金额：5050.00，购买金额排序：27},{产品类型:存款，产品名称：1到3年期大额存单，购买人数：2，购买人数排序：12，购买金额：700000.00，购买金额排序：2},{产品类型:理财，产品名称：南银理财鑫逸稳一年257期-B份额，购买人数：1，购买人数排序：29，购买金额：300000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -1465,7 +1465,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "客群范围": "有效通话客户"
   "购买存款人数": 46
   "新资金引入人数": 40
@@ -1479,7 +1479,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "客群范围": "有效通话客户"
   "购买理财人数": 54
   "新资金引入人数": 37
@@ -1494,7 +1494,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "外呼人数": 6538
   "外呼3日后金融资产提升人数": 1428
   "外呼7日后金融资产提升人数": 2290
@@ -1528,7 +1528,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "外呼人数": 3695
   "外呼3日后金融资产提升人数": 855
   "外呼7日后金融资产提升人数": 1347
@@ -1562,7 +1562,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "外呼人数": 2843
   "外呼3日后金融资产提升人数": 573
   "外呼7日后金融资产提升人数": 943
@@ -1596,7 +1596,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906568"
-  "act_name": "26.1泰州无锡·新开户存款意向客群"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群"
   "外呼人数": 4849
   "外呼3日后金融资产提升人数": 1067
   "外呼7日后金融资产提升人数": 1748
@@ -1640,7 +1640,7 @@
   "act_proc_no": "ACT2026011690656901"
   "push_task_name": "26年1月无新开户有存款意向"
   "push_task_remark": "开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
@@ -1658,7 +1658,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "yewu_type": "财富类"
   "外呼执行天数": 59
   "外呼人数": 7538
@@ -1685,7 +1685,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "外呼人数": 7538
   "外呼7日内点击理财人数": 351
   "外呼7日内购买理财人数": 76
@@ -1705,7 +1705,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "联系失败人数": 2843
   "外呼7日内点击理财人数": 120
   "外呼7日内购买理财人数": 24
@@ -1725,7 +1725,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "有效通话人数": 3695
   "外呼7日内点击理财人数": 231
   "外呼7日内购买理财人数": 52
@@ -1745,7 +1745,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "有效通话人数": 4849
   "外呼7日内点击理财人数": 260
   "外呼7日内购买理财人数": 57
@@ -1764,7 +1764,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "购买产品top10": "{产品类型:存款，产品名称：1到3年期普通定期，购买人数：39，购买人数排序：1，购买金额：3014525.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有7天11号-A份额（南京银行行庆专属），购买人数：19，购买人数排序：2，购买金额：327817.00，购买金额排序：4},{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额（南京银行行庆专属），购买人数：7，购买人数排序：3，购买金额：530000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财财富牛最低持有28天1号-A份额，购买人数：7，购买人数排序：4，购买金额：86717.00，购买金额排序：9},{产品类型:存款，产品名称：1年以内普通定期，购买人数：5，购买人数排序：5，购买金额：185150.00，购买金额排序：6},{产品类型:理财，产品名称：南银理财日日聚宝12号-A份额，购买人数：3，购买人数排序：6，购买金额：17839.00，购买金额排序：23},{产品类型:理财，产品名称：南银理财悦稳最低持有60天4号-A份额，购买人数：2，购买人数排序：7，购买金额：17899.00，购买金额排序：22},{产品类型:理财，产品名称：南银理财鼎瑞悦稳天添盈4号-A份额，购买人数：2，购买人数排序：8，购买金额：11347.00，购买金额排序：26},{产品类型:理财，产品名称：南银理财悦稳最低持有14天4号-A份额，购买人数：2，购买人数排序：9，购买金额：20000.00，购买金额排序：20},{产品类型:理财，产品名称：南银理财日日聚宝4号-A份额，购买人数：2，购买人数排序：10，购买金额：5050.00，购买金额排序：27},{产品类型:存款，产品名称：1到3年期大额存单，购买人数：2，购买人数排序：12，购买金额：700000.00，购买金额排序：2},{产品类型:理财，产品名称：南银理财鑫逸稳一年257期-B份额，购买人数：1，购买人数排序：29，购买金额：300000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -1773,7 +1773,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "客群范围": "有效通话客户"
   "购买存款人数": 46
   "新资金引入人数": 40
@@ -1787,7 +1787,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "客群范围": "有效通话客户"
   "购买理财人数": 54
   "新资金引入人数": 37
@@ -1802,7 +1802,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "外呼人数": 7538
   "外呼3日后金融资产提升人数": 1428
   "外呼7日后金融资产提升人数": 2290
@@ -1836,7 +1836,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "外呼人数": 4695
   "外呼3日后金融资产提升人数": 855
   "外呼7日后金融资产提升人数": 1347
@@ -1870,7 +1870,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "外呼人数": 3843
   "外呼3日后金融资产提升人数": 573
   "外呼7日后金融资产提升人数": 943
@@ -1904,7 +1904,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906569"
-  "act_name": "26.1泰州无锡·新开户存款意向客群B"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群B"
   "外呼人数": 5849
   "外呼3日后金融资产提升人数": 1067
   "外呼7日后金融资产提升人数": 1748
@@ -1948,7 +1948,7 @@
   "act_proc_no": "ACT2026011690657001"
   "push_task_name": "26年1月无新开户有存款意向"
   "push_task_remark": "开户时间为25年7月1日之后，有存款意向客户，推荐存款产品，注意区分存款利率地区差异"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "活动审核通过时间": "2026-01-16 16:53:55"
   "活动开始时间": "2026-01-17 00:05:00"
   "活动结束时间": "2026-01-31 23:59:59"
@@ -1966,7 +1966,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "yewu_type": "财富类"
   "外呼执行天数": 59
   "外呼人数": 8538
@@ -1993,7 +1993,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "外呼人数": 8538
   "外呼7日内点击理财人数": 351
   "外呼7日内购买理财人数": 76
@@ -2013,7 +2013,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "联系失败人数": 2843
   "外呼7日内点击理财人数": 120
   "外呼7日内购买理财人数": 24
@@ -2033,7 +2033,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "有效通话人数": 3695
   "外呼7日内点击理财人数": 231
   "外呼7日内购买理财人数": 52
@@ -2053,7 +2053,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "有效通话人数": 4849
   "外呼7日内点击理财人数": 260
   "外呼7日内购买理财人数": 57
@@ -2072,7 +2072,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "购买产品top10": "{产品类型:存款，产品名称：1到3年期普通定期，购买人数：39，购买人数排序：1，购买金额：3014525.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有7天11号-A份额（南京银行行庆专属），购买人数：19，购买人数排序：2，购买金额：327817.00，购买金额排序：4},{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额（南京银行行庆专属），购买人数：7，购买人数排序：3，购买金额：530000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财财富牛最低持有28天1号-A份额，购买人数：7，购买人数排序：4，购买金额：86717.00，购买金额排序：9},{产品类型:存款，产品名称：1年以内普通定期，购买人数：5，购买人数排序：5，购买金额：185150.00，购买金额排序：6},{产品类型:理财，产品名称：南银理财日日聚宝12号-A份额，购买人数：3，购买人数排序：6，购买金额：17839.00，购买金额排序：23},{产品类型:理财，产品名称：南银理财悦稳最低持有60天4号-A份额，购买人数：2，购买人数排序：7，购买金额：17899.00，购买金额排序：22},{产品类型:理财，产品名称：南银理财鼎瑞悦稳天添盈4号-A份额，购买人数：2，购买人数排序：8，购买金额：11347.00，购买金额排序：26},{产品类型:理财，产品名称：南银理财悦稳最低持有14天4号-A份额，购买人数：2，购买人数排序：9，购买金额：20000.00，购买金额排序：20},{产品类型:理财，产品名称：南银理财日日聚宝4号-A份额，购买人数：2，购买人数排序：10，购买金额：5050.00，购买金额排序：27},{产品类型:存款，产品名称：1到3年期大额存单，购买人数：2，购买人数排序：12，购买金额：700000.00，购买金额排序：2},{产品类型:理财，产品名称：南银理财鑫逸稳一年257期-B份额，购买人数：1，购买人数排序：29，购买金额：300000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -2081,7 +2081,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "客群范围": "有效通话客户"
   "购买存款人数": 46
   "新资金引入人数": 40
@@ -2095,7 +2095,7 @@
         <is>
           <t>{
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "客群范围": "有效通话客户"
   "购买理财人数": 54
   "新资金引入人数": 37
@@ -2110,7 +2110,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "外呼人数": 8538
   "外呼3日后金融资产提升人数": 1428
   "外呼7日后金融资产提升人数": 2290
@@ -2144,7 +2144,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "外呼人数": 5695
   "外呼3日后金融资产提升人数": 855
   "外呼7日后金融资产提升人数": 1347
@@ -2178,7 +2178,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "外呼人数": 4843
   "外呼3日后金融资产提升人数": 573
   "外呼7日后金融资产提升人数": 943
@@ -2212,7 +2212,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20260116906570"
-  "act_name": "26.1泰州无锡·新开户存款意向客群C"
+  "act_name": "DEMO-26.1泰州无锡·新开户存款意向客群C"
   "外呼人数": 6849
   "外呼3日后金融资产提升人数": 1067
   "外呼7日后金融资产提升人数": 1748
@@ -2256,7 +2256,7 @@
   "act_proc_no": "ACT2025060510481201"
   "push_task_name": "25年6月理财到期客户承接"
   "push_task_remark": "针对6月理财产品到期客户进行外呼触达，引导到期资金续投承接，推荐同风险等级续投产品"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "活动审核通过时间": "2025-06-04 15:22:10"
   "活动开始时间": "2025-06-04 15:22:10"
   "活动结束时间": "2025-06-30 23:59:59"
@@ -2274,7 +2274,7 @@
         <is>
           <t>{
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "yewu_type": "财富类"
   "外呼执行天数": 25
   "外呼人数": 10880
@@ -2301,7 +2301,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "外呼人数": 10880
   "外呼7日内点击理财人数": 890
   "外呼7日内购买理财人数": 260
@@ -2321,7 +2321,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "联系失败人数": 4896
   "外呼7日内点击理财人数": 360
   "外呼7日内购买理财人数": 92
@@ -2341,7 +2341,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "有效通话人数": 5984
   "外呼7日内点击理财人数": 530
   "外呼7日内购买理财人数": 168
@@ -2361,7 +2361,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "有效通话人数": 5266
   "外呼7日内点击理财人数": 480
   "外呼7日内购买理财人数": 152
@@ -2380,7 +2380,7 @@
         <is>
           <t>{
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "购买产品top10": "{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额，购买人数：58，购买人数排序：1，购买金额：28600000.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有7天11号-A份额，购买人数：44，购买人数排序：2，购买金额：15200000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财财富牛最低持有28天1号-A份额，购买人数：21，购买人数排序：3，购买金额：9800000.00，购买金额排序：4},{产品类型:存款，产品名称：1到3年期大额存单，购买人数：18，购买人数排序：4，购买金额：21500000.00，购买金额排序：2},{产品类型:理财，产品名称：南银理财日日聚宝12号-A份额，购买人数：11，购买人数排序：5，购买金额：4600000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -2389,7 +2389,7 @@
         <is>
           <t>{
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "客群范围": "有效通话客户"
   "购买存款人数": 56
   "新资金引入人数": 44
@@ -2403,7 +2403,7 @@
         <is>
           <t>{
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "客群范围": "有效通话客户"
   "购买理财人数": 152
   "新资金引入人数": 98
@@ -2418,7 +2418,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "外呼人数": 10880
   "外呼3日后金融资产提升人数": 2600
   "外呼7日后金融资产提升人数": 4100
@@ -2452,7 +2452,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "外呼人数": 5984
   "外呼3日后金融资产提升人数": 1620
   "外呼7日后金融资产提升人数": 2580
@@ -2486,7 +2486,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "外呼人数": 4896
   "外呼3日后金融资产提升人数": 980
   "外呼7日后金融资产提升人数": 1520
@@ -2520,7 +2520,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250605104812"
-  "act_name": "25年6月理财到期客户承接专项"
+  "act_name": "DEMO-25年6月理财到期客户承接专项"
   "外呼人数": 5266
   "外呼3日后金融资产提升人数": 1258
   "外呼7日后金融资产提升人数": 1984
@@ -2564,7 +2564,7 @@
   "act_proc_no": "ACT2025041010412601"
   "push_task_name": "25年Q2理财到期客户续投"
   "push_task_remark": "面向二季度理财产品到期客户外呼推荐续投产品及组合配置，防止到期资金流失"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "活动审核通过时间": "2025-04-09 10:08:45"
   "活动开始时间": "2025-04-09 10:08:45"
   "活动结束时间": "2025-05-10 23:59:59"
@@ -2582,7 +2582,7 @@
         <is>
           <t>{
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "yewu_type": "财富类"
   "外呼执行天数": 30
   "外呼人数": 7310
@@ -2609,7 +2609,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "外呼人数": 7310
   "外呼7日内点击理财人数": 720
   "外呼7日内购买理财人数": 228
@@ -2629,7 +2629,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "联系失败人数": 3110
   "外呼7日内点击理财人数": 290
   "外呼7日内购买理财人数": 82
@@ -2649,7 +2649,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "有效通话人数": 4200
   "外呼7日内点击理财人数": 430
   "外呼7日内购买理财人数": 146
@@ -2669,7 +2669,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "有效通话人数": 3680
   "外呼7日内点击理财人数": 390
   "外呼7日内购买理财人数": 132
@@ -2688,7 +2688,7 @@
         <is>
           <t>{
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "购买产品top10": "{产品类型:理财，产品名称：南银理财鑫逸稳一年257期-B份额，购买人数：46，购买人数排序：1，购买金额：32800000.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额，购买人数：38，购买人数排序：2，购买金额：18400000.00，购买金额排序：2},{产品类型:理财，产品名称：南银理财鼎瑞悦稳天添盈4号-A份额，购买人数：19，购买人数排序：3，购买金额：6200000.00，购买金额排序：4},{产品类型:存款，产品名称：1到3年期普通定期，购买人数：15，购买人数排序：4，购买金额：7800000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财日日聚宝4号-A份额，购买人数：8，购买人数排序：5，购买金额：2100000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -2697,7 +2697,7 @@
         <is>
           <t>{
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "客群范围": "有效通话客户"
   "购买存款人数": 42
   "新资金引入人数": 33
@@ -2711,7 +2711,7 @@
         <is>
           <t>{
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "客群范围": "有效通话客户"
   "购买理财人数": 132
   "新资金引入人数": 82
@@ -2726,7 +2726,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "外呼人数": 7310
   "外呼3日后金融资产提升人数": 1980
   "外呼7日后金融资产提升人数": 3260
@@ -2760,7 +2760,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "外呼人数": 4200
   "外呼3日后金融资产提升人数": 1220
   "外呼7日后金融资产提升人数": 2050
@@ -2794,7 +2794,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "外呼人数": 3110
   "外呼3日后金融资产提升人数": 760
   "外呼7日后金融资产提升人数": 1210
@@ -2828,7 +2828,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250410104126"
-  "act_name": "25年Q2理财到期客户续投专项活动"
+  "act_name": "DEMO-25年Q2理财到期客户续投专项活动"
   "外呼人数": 3680
   "外呼3日后金融资产提升人数": 996
   "外呼7日后金融资产提升人数": 1641
@@ -2872,7 +2872,7 @@
   "act_proc_no": "ACT2025052010460501"
   "push_task_name": "25年理财到期高净值客户资金承接"
   "push_task_remark": "针对高净值客户理财到期资金一对一外呼，提供专属承接与再配置方案，主推中长期理财及大额存单"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "活动审核通过时间": "2025-05-19 14:36:20"
   "活动开始时间": "2025-05-19 14:36:20"
   "活动结束时间": "2025-06-20 23:59:59"
@@ -2890,7 +2890,7 @@
         <is>
           <t>{
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "yewu_type": "财富类"
   "外呼执行天数": 32
   "外呼人数": 2880
@@ -2917,7 +2917,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "外呼人数": 2880
   "外呼7日内点击理财人数": 410
   "外呼7日内购买理财人数": 148
@@ -2937,7 +2937,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "联系失败人数": 980
   "外呼7日内点击理财人数": 140
   "外呼7日内购买理财人数": 44
@@ -2957,7 +2957,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "有效通话人数": 1900
   "外呼7日内点击理财人数": 270
   "外呼7日内购买理财人数": 104
@@ -2977,7 +2977,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "有效通话人数": 1700
   "外呼7日内点击理财人数": 250
   "外呼7日内购买理财人数": 98
@@ -2996,7 +2996,7 @@
         <is>
           <t>{
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "购买产品top10": "{产品类型:理财，产品名称：南银理财鑫逸稳一年257期-B份额，购买人数：32，购买人数排序：1，购买金额：48600000.00，购买金额排序：1},{产品类型:理财，产品名称：南银理财悦稳最低持有189天3号-A份额，购买人数：24，购买人数排序：2，购买金额：31200000.00，购买金额排序：2},{产品类型:存款，产品名称：1到3年期大额存单，购买人数：9，购买人数排序：3，购买金额：18600000.00，购买金额排序：3},{产品类型:理财，产品名称：南银理财财富牛最低持有28天1号-A份额，购买人数：7，购买人数排序：4，购买金额：5400000.00，购买金额排序：4},{产品类型:理财，产品名称：南银理财悦稳最低持有60天4号-A份额，购买人数：4，购买人数排序：5，购买金额：2800000.00，购买金额排序：5}"
 }</t>
         </is>
@@ -3005,7 +3005,7 @@
         <is>
           <t>{
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "客群范围": "有效通话客户"
   "购买存款人数": 32
   "新资金引入人数": 22
@@ -3019,7 +3019,7 @@
         <is>
           <t>{
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "客群范围": "有效通话客户"
   "购买理财人数": 98
   "新资金引入人数": 48
@@ -3034,7 +3034,7 @@
           <t>{
   "客群范围": "外呼所有客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "外呼人数": 2880
   "外呼3日后金融资产提升人数": 720
   "外呼7日后金融资产提升人数": 1280
@@ -3068,7 +3068,7 @@
           <t>{
   "客群范围": "联系成功客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "外呼人数": 1900
   "外呼3日后金融资产提升人数": 480
   "外呼7日后金融资产提升人数": 860
@@ -3102,7 +3102,7 @@
           <t>{
   "客群范围": "联系失败客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "外呼人数": 980
   "外呼3日后金融资产提升人数": 240
   "外呼7日后金融资产提升人数": 420
@@ -3136,7 +3136,7 @@
           <t>{
   "客群范围": "有效通话客户"
   "act_no": "ACT20250520104605"
-  "act_name": "25年理财到期资金承接·高净值客户专班"
+  "act_name": "DEMO-25年理财到期资金承接·高净值客户专班"
   "外呼人数": 1700
   "外呼3日后金融资产提升人数": 425
   "外呼7日后金融资产提升人数": 755
